--- a/output/provincial_validation_report.xlsx
+++ b/output/provincial_validation_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12T09:48:56</t>
+          <t>2026-08-12T10:58:58</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -569,47 +569,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>天津市 - 一致确认</t>
+          <t>湖南省 - 一致确认</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>天津市 - 低置信度(疑似OCR串块,需人工核对)</t>
+          <t>重庆市 - celma未收录</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>湖南省 - 一致确认</t>
+          <t>重庆市 - 低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>重庆市 - celma未收录</t>
+          <t>山东省 - 一致确认</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>重庆市 - 低置信度(疑似OCR串块,需人工核对)</t>
+          <t>青岛市 - 一致确认</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -619,20 +619,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>本次已自动修正-发行规模</t>
+          <t>青岛市 - celma未收录</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>青岛市 - 低置信度(疑似OCR串块,需人工核对)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>河南省 - 低置信度(疑似OCR串块,需人工核对)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>本次已自动修正-发行规模</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>本次已自动修正-票面利率</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -681,83 +711,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>40%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>黑龙江省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>陕西省</t>
+          <t>黑龙江省</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>陕西省</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -771,11 +801,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -789,11 +819,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -807,11 +837,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>吉林省</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -825,11 +855,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>宁夏回族自治区</t>
+          <t>吉林省</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -843,11 +873,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>宁夏回族自治区</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -861,7 +891,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>宁波市</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -879,11 +909,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -897,11 +927,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>湖南省</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -915,11 +945,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>湖南省</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -933,11 +963,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -951,11 +981,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>江西省</t>
+          <t>河北省</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -969,11 +999,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -987,11 +1017,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1005,11 +1035,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1023,7 +1053,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1103,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1143,106 +1173,295 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26内蒙18</t>
+          <t>26河南58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>237574</t>
+          <t>237584</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>关于2026年内蒙古自治区政府再融资一般债券（七期）上市交易的通知</t>
+          <t>关于2026年河南省政府专项债券（五十期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26内蒙19</t>
+          <t>26河南59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>237575</t>
+          <t>237585</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>关于2026年内蒙古自治区政府再融资专项债券（七期）上市交易的通知</t>
+          <t>关于2026年河南省政府专项债券（五十一期)上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26龙江22</t>
+          <t>26河南60</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>237556</t>
+          <t>237586</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>黑龙江省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>关于2026年黑龙江省政府一般债券（四期）上市交易的通知</t>
+          <t>关于2026年河南省政府专项债券（五十二期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>26河南61</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>237587</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>关于2026年河南省政府专项债券（五十三期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>26广东44</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>237588</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>关于2026年广东省政府一般债券 （七期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>26广东45</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>237589</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>关于2026年广东省政府专项债券（三十八期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>26广东46</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>237590</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>关于2026年广东省政府专项债券（三十九期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>26内蒙18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>237574</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>内蒙古自治区</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>关于2026年内蒙古自治区政府再融资一般债券（七期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>26内蒙19</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>237575</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>内蒙古自治区</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>关于2026年内蒙古自治区政府再融资专项债券（七期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>26龙江22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>237556</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>黑龙江省</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>关于2026年黑龙江省政府一般债券（四期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>26龙江23</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>237557</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>黑龙江省</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>关于2026年黑龙江省政府再融资一般债券（三期）上市交易的通知</t>
         </is>
@@ -1259,7 +1478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2072,7 +2291,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>湖南省</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2080,9 +2299,14 @@
           <t>一致确认</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026年湖南省地方政府再融资专项债券（七期）</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2090,27 +2314,33 @@
           <t>7Y</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.62</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>26天津债54</t>
+          <t>26湖南债26</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>31.36</v>
+        <v>11.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202608/t20260804_7347170.html</t>
+          <t>https://czt.hunan.gov.cn/czt/dzqzfzjxx/202607/t20260727_34034503.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>湖南省</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2118,203 +2348,191 @@
           <t>一致确认</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026年湖南省地方政府再融资专项债券（八期）</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20Y</t>
-        </is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.62</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>26天津46</t>
+          <t>26湖南债27</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>350</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>https://czt.hunan.gov.cn/czt/dzqzfzjxx/202607/t20260727_34034503.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>26天津49</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.34</v>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>30Y</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4支天津市债券在2026-08-04同为30Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
+          <t>row itself missing issue_date/term, cannot match</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202608/t20260804_7347170.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>30Y</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4支天津市债券在2026-08-04同为30Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
+          <t>row itself missing issue_date/term, cannot match</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202608/t20260804_7347170.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>30Y</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4支天津市债券在2026-08-04同为30Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
+          <t>row itself missing issue_date/term, cannot match</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202608/t20260804_7347170.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>celma未收录</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026年重庆市地方政府再融资专项债券十一期)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>30Y</t>
-        </is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>2.31</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4支天津市债券在2026-08-04同为30Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
+          <t>row itself missing issue_date/term, cannot match</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202608/t20260804_7347170.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2322,140 +2540,192 @@
           <t>低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>计划发行规模到期日2026年重庆市政府专项债券《二十一期)99.78亿元实际发行规模99.78亿元发行价格100元付息频率6月/次日(节假日顺延)2026年重庆市土地储备专项债券(二期)-2026年重庆市政府专项债券(二十二期)38.45亿元实际发行规模38,45亿元</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7Y</t>
-        </is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>99.78</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3支天津市债券在2026-07-07同为7Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
+          <t>债券名称字段内混入了'债券代码/存续期/票面利率'等字段标签文本，疑似OCR丢失中间'债券名称'标签导致多支债券的标题和字段被合并进同一分块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026年山东省政府专项债券（四十二期）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2支天津市债券在2026-07-07同为5Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>26山东债77</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.62</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026年山东省政府专项债券（四十三期）</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7Y</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>3支天津市债券在2026-07-07同为7Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>26山东债78</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.34</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026年山东省政府专项债券（四十四期）</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7Y</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>3支天津市债券在2026-07-07同为7Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+          <t>15Y</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>26山东债79</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026年山东省政府专项债券（四十五期）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2463,98 +2733,137 @@
           <t>10Y</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>3支天津市债券在2026-07-07同为10Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+      <c r="F29" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>26山东债80</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.78</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026年山东省政府专项债券（四十六期）</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>30Y</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>3支天津市债券在2026-07-07同为30Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>26山东债81</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.78</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026年山东省政府专项债券（四十七期）</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>30Y</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>3支天津市债券在2026-07-07同为30Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+          <t>15Y</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>26山东债82</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.15</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026年山东省地方政府再融资专项债券（二十六期）</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2562,95 +2871,137 @@
           <t>10Y</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>3支天津市债券在2026-07-07同为10Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+      <c r="F32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>26山东74</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.79</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/15/art_10559_10330745.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026年山东省地方政府再融资专项债券（二十七期）</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2支天津市债券在2026-07-07同为5Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+          <t>15Y</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>26山东75</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.15</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/15/art_10559_10330745.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026年山东省地方政府再融资专项债券（二十八期）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>3支天津市债券在2026-07-07同为10Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>26山东76</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.4</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://czt.shandong.gov.cn/art/2026/7/15/art_10559_10330745.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>一致确认</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026年青岛市政府专项债券(三十六期)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2658,119 +3009,87 @@
           <t>30Y</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>3支天津市债券在2026-07-07同为30Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
+      <c r="F35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>26青岛债62</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.4</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://cz.tj.gov.cn/zwgk_53713/zfzq/202607/t20260707_7331606.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>湖南省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>一致确认</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026年湖南省地方政府再融资专项债券（七期）</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>7Y</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>26湖南债26</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1.62</v>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://czt.hunan.gov.cn/czt/dzqzfzjxx/202607/t20260727_34034503.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>湖南省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>一致确认</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026年湖南省地方政府再融资专项债券（八期）</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>7Y</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>350</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>26湖南债27</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>350</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1.62</v>
+        <v>51.9</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://czt.hunan.gov.cn/czt/dzqzfzjxx/202607/t20260727_34034503.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2778,10 +3097,18 @@
           <t>celma未收录</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026年青岛市政府专项债券(三十三期)</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>2.38</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2790,14 +3117,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2807,7 +3134,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2817,14 +3144,14 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2834,8 +3161,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>20.55</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2844,76 +3174,91 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>celma未收录</t>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026年青岛市政府专项债券(三十四期)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>2.38</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>2支青岛市债券在2026-07-20同为20Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>celma未收录</t>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026年重庆市地方政府再融资专项债券十一期)</t>
+          <t>2026年青岛市政府专项债券(三十七期)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>2.31</v>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>3支青岛市债券在2026-07-20同为10Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2923,30 +3268,143 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>计划发行规模到期日2026年重庆市政府专项债券《二十一期)99.78亿元实际发行规模99.78亿元发行价格100元付息频率6月/次日(节假日顺延)2026年重庆市土地储备专项债券(二期)-2026年重庆市政府专项债券(二十二期)38.45亿元实际发行规模38,45亿元</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+          <t>俩关税和由26河南债58债券编码199059</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>99.78</v>
+        <v>44.52</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.76</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>债券名称字段内混入了'债券代码/存续期/票面利率'等字段标签文本，疑似OCR丢失中间'债券名称'标签导致多支债券的标题和字段被合并进同一分块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
+          <t>文档内含1处债券简称但只切分出2个债券名称分块，疑似OCR识别丢失部分'债券名称'标签导致相邻债券字段串块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://czt.henan.gov.cn/2026/08-11/3397843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>省政府专项债券(五十二期)债券简称</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>文档内含1处债券简称但只切分出2个债券名称分块，疑似OCR识别丢失部分'债券名称'标签导致相邻债券字段串块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>http://czt.henan.gov.cn/2026/08-11/3397843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026年河南省棚改专项债券(十三期)一一2026年河南省政府]专项债券(四十四期)债券简称26河南5债券编码“236787</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>文档内含6处债券简称但只切分出2个债券名称分块，疑似OCR识别丢失部分'债券名称'标签导致相邻债券字段串块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>http://czt.henan.gov.cn/2026/07-23/3378602.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>河南省</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026年河南省政府专项债券(四十八期)债券简称26河南56债差编码236791]计划交行规模。2全人元实际发行规模62.41亿元]发行期限30年其票面利率2.36多发行价格100元付意频率按半年付息每年1月24日、7月24日到期日2056年7月24日七期)一一2026年河南债券简称26河南57债券编码236792</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>文档内含6处债券简称但只切分出2个债券名称分块，疑似OCR识别丢失部分'债券名称'标签导致相邻债券字段串块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>http://czt.henan.gov.cn/2026/07-23/3378602.html</t>
         </is>
       </c>
     </row>

--- a/output/provincial_validation_report.xlsx
+++ b/output/provincial_validation_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12T10:58:58</t>
+          <t>2026-08-25T15:48:19</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14951</v>
+        <v>14998</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6">
@@ -493,23 +493,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>上海市 - 一致确认</t>
+          <t>河北省 - celma未收录</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>河北省 - celma未收录</t>
+          <t>河北省 - 低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -519,37 +519,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>河北省 - 低置信度(疑似OCR串块,需人工核对)</t>
+          <t>湖南省 - 一致确认</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>贵州省 - 一致确认</t>
+          <t>重庆市 - celma未收录</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>江苏省 - 一致确认</t>
+          <t>青岛市 - celma未收录</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>江苏省 - celma未收录</t>
+          <t>青岛市 - 低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -559,110 +559,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>宁夏回族自治区 - 一致确认</t>
+          <t>河南省 - 一致确认</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>湖南省 - 一致确认</t>
+          <t>河南省 - celma未收录</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>重庆市 - celma未收录</t>
+          <t>河南省 - 低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>重庆市 - 低置信度(疑似OCR串块,需人工核对)</t>
+          <t>本次已自动修正-发行规模</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>山东省 - 一致确认</t>
+          <t>本次已自动修正-票面利率</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>青岛市 - 一致确认</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>青岛市 - celma未收录</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>青岛市 - 低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>河南省 - 低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>本次已自动修正-发行规模</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>本次已自动修正-票面利率</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -677,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -711,50 +651,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>75%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>山西省</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -765,14 +705,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>黑龙江省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -783,47 +723,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>陕西省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>陕西省</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -841,7 +781,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -855,11 +795,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>吉林省</t>
+          <t>青海省</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -873,7 +813,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>宁夏回族自治区</t>
+          <t>湖南省</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -891,11 +831,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>海南省</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -909,11 +849,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -927,11 +867,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>甘肃省</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -945,11 +885,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>湖南省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -963,11 +903,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -981,7 +921,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -999,11 +939,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>江西省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1017,11 +957,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1035,11 +975,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1053,70 +993,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>吉林省</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>浙江省</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>10</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>6</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>青岛市</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>10</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1133,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1173,297 +1059,1458 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26河南58</t>
+          <t>26江西39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>237584</t>
+          <t>236820</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>关于2026年河南省政府专项债券（五十期）上市交易的通知</t>
+          <t>关于2026年江西省政府专项债券（二十六期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26河南59</t>
+          <t>26江西40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>237585</t>
+          <t>236821</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>关于2026年河南省政府专项债券（五十一期)上市交易的通知</t>
+          <t>关于2026年江西省政府专项债券（二十七期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26河南60</t>
+          <t>26江西41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>237586</t>
+          <t>236822</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>关于2026年河南省政府专项债券（五十二期）上市交易的通知</t>
+          <t>关于2026年江西省政府专项债券（二十八期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26河南61</t>
+          <t>26江西42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>237587</t>
+          <t>236823</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>关于2026年河南省政府专项债券（五十三期）上市交易的通知</t>
+          <t>关于2026年江西省地方政府再融资一般债券（五期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26广东44</t>
+          <t>26江西43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>237588</t>
+          <t>236824</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>关于2026年广东省政府一般债券 （七期）上市交易的通知</t>
+          <t>关于2026年江西省地方政府再融资一般债券（六期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26广东45</t>
+          <t>26江西44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>237589</t>
+          <t>236825</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>关于2026年广东省政府专项债券（三十八期）上市交易的通知</t>
+          <t>关于2026年江西省地方政府再融资专项债券（八期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26广东46</t>
+          <t>26江西45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>237590</t>
+          <t>236826</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>关于2026年广东省政府专项债券（三十九期）上市交易的通知</t>
+          <t>关于2026年江西省地方政府再融资专项债券（九期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26内蒙18</t>
+          <t>26江西46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>237574</t>
+          <t>236827</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>关于2026年内蒙古自治区政府再融资一般债券（七期）上市交易的通知</t>
+          <t>关于2026年江西省地方政府再融资专项债券（十期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26内蒙19</t>
+          <t>26青岛67</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>237575</t>
+          <t>237678</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>关于2026年内蒙古自治区政府再融资专项债券（七期）上市交易的通知</t>
+          <t>关于2026年青岛市政府专项债券（三十九期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26龙江22</t>
+          <t>26青岛68</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>237556</t>
+          <t>237679</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>黑龙江省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>关于2026年黑龙江省政府一般债券（四期）上市交易的通知</t>
+          <t>关于2026年青岛市政府专项债券（四十期）上市交易的通知</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26龙江23</t>
+          <t>26青岛69</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>237557</t>
+          <t>237680</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>黑龙江省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>关于2026年黑龙江省政府再融资一般债券（三期）上市交易的通知</t>
+          <t>关于2026年青岛市政府专项债券（四十一期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>26青岛70</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>237681</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府专项债券（四十二期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>26青岛71</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>237682</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府专项债券（四十三期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>26青岛72</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>237683</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府专项债券（四十四期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>26青岛73</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>237684</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府专项债券（四十五期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>26青岛74</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>237685</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府专项债券（四十六期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>26青岛75</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>237686</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府专项债券（四十七期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>26青岛76</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>237687</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府专项债券（四十八期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>26青岛77</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>237688</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府再融资一般债券（八期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>26青岛78</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>237689</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府再融资一般债券（九期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>26青岛79</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府再融资专项债券（十七期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>26青岛80</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>237691</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>关于2026年青岛市政府再融资专项债券（十八期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>26山东87</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>237661</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>关于2026年山东省政府专项债券（五十一期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>26山东88</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>237662</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>关于2026年山东省政府专项债券（五十二期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>26山东89</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>237663</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>关于2026年山东省政府专项债券（五十三期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26山东90</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>237664</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>关于2026年山东省政府专项债券（五十四期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>26山东91</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>237665</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>关于2026年山东省政府专项债券（五十五期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>26山东92</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>237666</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>关于2026年山东省政府专项债券（五十六期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>26山东93</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>237667</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>关于2026年山东省政府一般债券（三期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>26山东94</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>237668</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>关于2026年山东省地方政府再融资一般债券（七期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>26山东95</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>237669</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>关于2026年山东省地方政府再融资专项债券（二十九期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>26山东96</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>237670</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>关于2026年山东省地方政府再融资专项债券（三十期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>26山东97</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>237671</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>关于2026年山东省地方政府再融资专项债券（三十一期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>26山东98</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>237672</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>关于2026年山东省地方政府再融资专项债券（三十二期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>26山西43</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>237651</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府一般债券（五期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>26山西44</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>237652</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府一般债券（六期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>26山西45</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>237653</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府专项债券（三十三期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>26山西46</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>237654</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府专项债券（三十四期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>26山西47</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>237655</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府专项债券（三十五期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>26山西48</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>237656</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府专项债券（三十六期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>26山西49</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>237657</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府专项债券（三十七期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>26山西50</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>237658</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府再融资专项债券（四期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>26山西51</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>237659</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府再融资专项债券（五期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>26山西52</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>237660</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>关于2026年山西省政府再融资专项债券（六期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>26辽宁37</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>237641</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>辽宁省</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>关于2026年辽宁省政府一般债券（三期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>26辽宁38</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>237642</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>辽宁省</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>关于2026年辽宁省政府专项债券（十七期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>26辽宁39</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>237643</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>辽宁省</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>关于2026年辽宁省政府专项债券（十八期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>26辽宁40</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>237644</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>辽宁省</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>关于2026年辽宁省政府专项债券（十九期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>26辽宁41</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>237645</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>辽宁省</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>关于2026年辽宁省地方政府再融资专项债券 (十一期)上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>26辽宁42</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>237646</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>辽宁省</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>关于2026年辽宁省地方政府再融资专项债券（十二期）上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>26陕西45</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>237604</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>陕西省</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>关于2026年陕西省政府专项债券(二十一期)上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>26陕西46</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>237605</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>陕西省</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>关于2026年陕西省政府专项债券(二十二期)上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>26陕西47</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>237606</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>陕西省</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>关于2026年陕西省政府专项债券(二十三期)上市交易的通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>26陕西43</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>237573</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>陕西省</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>关于2026年陕西省地方政府再融资专项债券(十一期)上市交易的通知</t>
         </is>
       </c>
     </row>
@@ -1478,7 +2525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1560,105 +2607,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>河北省</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>一致确认</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026年上海市政府再融资一般债券(一期)</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>26上海18</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.44</v>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://czj.sh.gov.cn/zys_8908/gsgg_8929/czywgg_8930/dfzwfxjg/20260713/xxfboswf0000003751.html</t>
+          <t>https://czt.hebei.gov.cn/root17/zfxx/202607/t20260720_2399072.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>河北省</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026年上海市政府再融资一般债券(二期)</t>
+          <t>2026年河北省政府再融资一般债券(七期)一22026年河北省政府一般债券(十期)债券代码260587026河北债41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>34.1151</v>
+        <v>65.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.799</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>26上海19</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>34.12</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>债券名称字段内混入了'债券代码/存续期/票面利率'等字段标签文本，疑似OCR丢失中间'债券名称'标签导致多支债券的标题和字段被合并进同一分块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://czj.sh.gov.cn/zys_8908/gsgg_8929/czywgg_8930/dfzwfxjg/20260713/xxfboswf0000003751.html</t>
+          <t>https://czt.hebei.gov.cn/root17/zfxx/202607/t20260720_2399072.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖南省</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1666,43 +2685,48 @@
           <t>一致确认</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026年湖南省地方政府再融资专项债券（七期）</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.2</v>
+        <v>11.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>26上海20</t>
+          <t>26湖南债26</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>11.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://czj.sh.gov.cn/zys_8908/gsgg_8929/czywgg_8930/dfzwfxjg/20260713/xxfboswf0000003751.html</t>
+          <t>https://czt.hunan.gov.cn/czt/dzqzfzjxx/202607/t20260727_34034503.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖南省</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1712,46 +2736,46 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026年上海市政府再融资专项债券〈(二期)</t>
+          <t>2026年湖南省地方政府再融资专项债券（八期）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>131</v>
+        <v>350</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>26上海21</t>
+          <t>26湖南债27</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>131</v>
+        <v>350</v>
       </c>
       <c r="J5" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://czj.sh.gov.cn/zys_8908/gsgg_8929/czywgg_8930/dfzwfxjg/20260713/xxfboswf0000003751.html</t>
+          <t>https://czt.hunan.gov.cn/czt/dzqzfzjxx/202607/t20260727_34034503.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1761,8 +2785,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>33.63</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1771,345 +2798,248 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://czt.hebei.gov.cn/root17/zfxx/202607/t20260720_2399072.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026年河北省政府再融资一般债券(七期)一22026年河北省政府一般债券(十期)债券代码260587026河北债41</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>65.52</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.49</v>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>债券名称字段内混入了'债券代码/存续期/票面利率'等字段标签文本，疑似OCR丢失中间'债券名称'标签导致多支债券的标题和字段被合并进同一分块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
+          <t>row itself missing issue_date/term, cannot match</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://czt.hebei.gov.cn/root17/zfxx/202607/t20260720_2399072.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>一致确认</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026年贵州省政府专项债券(一期)</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>30Y</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>163</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>26贵州债13</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>163</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.41</v>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://czt.guizhou.gov.cn/zwgk/zdlyxx/zfzw/202607/t20260709_90604174.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026年江苏省政府一般债券(二期)</t>
+          <t>日顺移)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>10Y</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>109</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>26江苏债31</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>109</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.79</v>
+        <v>38.45</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://czt.jiangsu.gov.cn/art/2026/7/24/art_77314_11808314.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>一致确认</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026年江苏省政府专项债券《十二期)</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>15Y</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>297</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>26江苏债32</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>297</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.08</v>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://czt.jiangsu.gov.cn/art/2026/7/24/art_77314_11808314.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026年江苏省地方政府再融资一般债券(五期)</t>
+          <t>2026年重庆市地方政府再融资专项债券十一期)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>16.01</v>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="G11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>26江苏债34</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.79</v>
+        <v>2.31</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://czt.jiangsu.gov.cn/art/2026/7/24/art_77314_11808312.html</t>
+          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026年江苏省地方政府再融资专项债券(十五期)</t>
+          <t>2026年青岛市政府专项债券(三十九期)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>350.07</v>
+        <v>5.2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>26江苏债35</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>350.07</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://czt.jiangsu.gov.cn/art/2026/7/24/art_77314_11808312.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026年江苏省地方政府再融资专项债券(十六期)</t>
+          <t>2026年青岛市政府专项债券(四十期)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20Y</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>55.66</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.269</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>26江苏债36</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>55.66</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://czt.jiangsu.gov.cn/art/2026/7/24/art_77314_11808312.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2119,47 +3049,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026年江苏省政府专项债券《十三期)</t>
+          <t>2026年青岛市政府专项债券(四十二期)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30Y</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>300</v>
+        <v>1.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.29</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>no state_results.csv row for this province/date/term</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://czt.jiangsu.gov.cn/art/2026/7/24/art_77314_11808314.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>宁夏回族自治区</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026年宁夏回族自治区政府再融资一般债券（四期）</t>
+          <t>2026年青岛市政府专项债券(四十三期)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2168,228 +3106,195 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>58.12</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>26宁夏债23</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>58.12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://czt.nx.gov.cn/xwzx/tzgg/202608/t20260807_5308161.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>宁夏回族自治区</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026年宁夏回族自治区政府再融资专项债券（四期）</t>
+          <t>2026年青岛市政府专项债券《四十四期)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>26宁夏债24</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://czt.nx.gov.cn/xwzx/tzgg/202608/t20260807_5308161.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>宁夏回族自治区</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026年宁夏回族自治区政府再融资专项债券（五期）</t>
+          <t>2026年青岛市政府专项债券(四十五期)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7.01</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>26宁夏债25</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.76</v>
+        <v>2.29</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://czt.nx.gov.cn/xwzx/tzgg/202608/t20260807_5308161.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>湖南省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026年湖南省地方政府再融资专项债券（七期）</t>
+          <t>2026年青岛市政府专项债券(四十六期)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11.6</v>
+        <v>6.46</v>
       </c>
       <c r="G18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>26湖南债26</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://czt.hunan.gov.cn/czt/dzqzfzjxx/202607/t20260727_34034503.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>湖南省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026年湖南省地方政府再融资专项债券（八期）</t>
+          <t>2026年青岛市政府专项债券(四十七期)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>350</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>26湖南债27</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>350</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://czt.hunan.gov.cn/czt/dzqzfzjxx/202607/t20260727_34034503.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2397,10 +3302,21 @@
           <t>celma未收录</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026年青岛市政府专项债券【四十八期)</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.29</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2409,14 +3325,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2424,26 +3340,39 @@
           <t>celma未收录</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026年青岛市政府再融资一般债券(八期)</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>47.98</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>no state_results.csv row for this province/date/term</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2451,26 +3380,42 @@
           <t>celma未收录</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026年豆岛市政府再融资一般债券(九期)</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>173</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>no state_results.csv row for this province/date/term</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2478,26 +3423,42 @@
           <t>celma未收录</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026年青岛市政府再融资专项债券〈十七期)</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.42</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>no state_results.csv row for this province/date/term</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2507,271 +3468,265 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026年重庆市地方政府再融资专项债券十一期)</t>
+          <t>2026年青岛市政府再融资专项债券(十八期)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>8.82</v>
       </c>
       <c r="G24" t="n">
-        <v>2.31</v>
+        <v>1.71</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>no state_results.csv row for this province/date/term</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202608/t20260824_10707685.shtml</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>计划发行规模到期日2026年重庆市政府专项债券《二十一期)99.78亿元实际发行规模99.78亿元发行价格100元付息频率6月/次日(节假日顺延)2026年重庆市土地储备专项债券(二期)-2026年重庆市政府专项债券(二十二期)38.45亿元实际发行规模38,45亿元</t>
+          <t>2026年青岛市政府一般债券(五期)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>99.78</v>
+        <v>51.9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.79</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>债券名称字段内混入了'债券代码/存续期/票面利率'等字段标签文本，疑似OCR丢失中间'债券名称'标签导致多支债券的标题和字段被合并进同一分块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
+          <t>no state_results.csv row for this province/date/term</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://czj.cq.gov.cn/zwgk_268/zfxxgkml/dfzfzw/202607/t20260729_15868828.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026年山东省政府专项债券（四十二期）</t>
+          <t>2026年青岛市政府专项债券(三十二期)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>26山东债77</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.62</v>
+        <v>0.4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026年山东省政府专项债券（四十三期）</t>
+          <t>2026年青岛市政府专项债券(三十三期)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>50.54</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>26山东债78</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>50.54</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.34</v>
+        <v>1.21</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026年山东省政府专项债券（四十四期）</t>
+          <t>2026年青岛市政府专项债券(三十四期)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>15Y</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>45.46</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>26山东债79</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>45.46</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.1</v>
+        <v>15</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>row itself missing issue_date/term, cannot match</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026年山东省政府专项债券（四十五期）</t>
+          <t>2026年青岛市政府专项债券(三十六期)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>26山东债80</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.78</v>
+        <v>3.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>celma未收录</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026年山东省政府专项债券（四十六期）</t>
+          <t>2026年青岛市政府专项债券(三十七期)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2779,76 +3734,58 @@
           <t>10Y</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>26山东债81</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.78</v>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>no state_results.csv row for this province/date/term</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>一致确认</t>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026年山东省政府专项债券（四十七期）</t>
+          <t>计划发行规模发行期限发行价格2.40%半年2056年7月21日</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15Y</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>26山东债82</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.15</v>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>债券名称字段内混入了'债券代码/存续期/票面利率'等字段标签文本，疑似OCR丢失中间'债券名称'标签导致多支债券的标题和字段被合并进同一分块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/28/art_10559_10330986.html</t>
+          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,12 +3795,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026年山东省地方政府再融资专项债券（二十六期）</t>
+          <t>2026年河南省政府专项债券(五十期)广一债券简称26河南债58债券编码199059_</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2872,29 +3809,29 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.54</v>
+        <v>44.52</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>26山东74</t>
+          <t>26河南债58</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.54</v>
+        <v>44.52</v>
       </c>
       <c r="J32" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/15/art_10559_10330745.html</t>
+          <t>http://czt.henan.gov.cn/2026/08-11/3397843.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2904,43 +3841,43 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026年山东省地方政府再融资专项债券（二十七期）</t>
+          <t>2026年河南省政府再融资专项债券(十八期)一一2026年河南省政府专项债券(五十一期)债券简称26河南债59债券凡199660</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>42.01</v>
+        <v>193.67</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>26山东75</t>
+          <t>26河南债59</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>42.01</v>
+        <v>193.67</v>
       </c>
       <c r="J33" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/15/art_10559_10330745.html</t>
+          <t>http://czt.henan.gov.cn/2026/08-11/3397843.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2950,43 +3887,43 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026年山东省地方政府再融资专项债券（二十八期）</t>
+          <t>2026年河南省棚改专项债券(十四期)一一2026年河南省政府专项债券(四十五期)债券简称26河南53责券编码236788</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>29.59</v>
+        <v>6.31</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>26山东76</t>
+          <t>26河南53</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>29.59</v>
+        <v>6.31</v>
       </c>
       <c r="J34" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>http://czt.shandong.gov.cn/art/2026/7/15/art_10559_10330745.html</t>
+          <t>http://czt.henan.gov.cn/2026/07-23/3378602.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2994,45 +3931,40 @@
           <t>一致确认</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026年青岛市政府专项债券(三十六期)</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>26青岛债62</t>
+          <t>26河南55</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
+          <t>http://czt.henan.gov.cn/2026/07-23/3378602.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3042,8 +3974,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>11.19</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3052,357 +3987,85 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
+          <t>http://czt.henan.gov.cn/2026/07-23/3378602.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>celma未收录</t>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026年河南省政府再融资专项债券(二十期)一一2026年河南省政府专项债券(五十三期)责券简称26河南债61债券编码199662</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10Y</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>51.9</v>
+        <v>44.56</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>4支河南省债券在2026-08-11同为10Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
+          <t>http://czt.henan.gov.cn/2026/08-11/3397843.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>celma未收录</t>
+          <t>低置信度(疑似OCR串块,需人工核对)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026年青岛市政府专项债券(三十三期)</t>
+          <t>人债券简称26河南56债券编码236791计划交行夫模62.41亿元62.41亿元]发行期限30年其票面利率2.36纹发行价格100元付息频率按半年付息每年1月24日、7月4日到期日2056年7月24日2026年河南省政府再融资专项债券(十七期)一一2026年河南，、全关各和省政府专项债券(四十九期)债券简称26河南57债券编码236792-本呈殉-了</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>2.38</v>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>4.32</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>row itself missing issue_date/term, cannot match</t>
+          <t>债券名称字段内混入了'债券代码/存续期/票面利率'等字段标签文本，疑似OCR丢失中间'债券名称'标签导致多支债券的标题和字段被合并进同一分块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
-        <is>
-          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>青岛市</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>celma未收录</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>row itself missing issue_date/term, cannot match</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>青岛市</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>celma未收录</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>row itself missing issue_date/term, cannot match</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>青岛市</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026年青岛市政府专项债券(三十四期)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>20Y</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>2支青岛市债券在2026-07-20同为20Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>青岛市</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026年青岛市政府专项债券(三十七期)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>3支青岛市债券在2026-07-20同为10Y期，且本行缺少可用于区分的发行规模，无法确认具体对应哪一支，需人工核对原文</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>http://qdcz.qingdao.gov.cn/zfxxgk/fdzdgknr/zdly/zwgl/202607/t20260720_10681232.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>河南省</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>俩关税和由26河南债58债券编码199059</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>文档内含1处债券简称但只切分出2个债券名称分块，疑似OCR识别丢失部分'债券名称'标签导致相邻债券字段串块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>http://czt.henan.gov.cn/2026/08-11/3397843.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>河南省</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>省政府专项债券(五十二期)债券简称</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>文档内含1处债券简称但只切分出2个债券名称分块，疑似OCR识别丢失部分'债券名称'标签导致相邻债券字段串块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>http://czt.henan.gov.cn/2026/08-11/3397843.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>河南省</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026年河南省棚改专项债券(十三期)一一2026年河南省政府]专项债券(四十四期)债券简称26河南5债券编码“236787</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>7Y</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>文档内含6处债券简称但只切分出2个债券名称分块，疑似OCR识别丢失部分'债券名称'标签导致相邻债券字段串块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>http://czt.henan.gov.cn/2026/07-23/3378602.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>河南省</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>低置信度(疑似OCR串块,需人工核对)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026年河南省政府专项债券(四十八期)债券简称26河南56债差编码236791]计划交行规模。2全人元实际发行规模62.41亿元]发行期限30年其票面利率2.36多发行价格100元付意频率按半年付息每年1月24日、7月24日到期日2056年7月24日七期)一一2026年河南债券简称26河南57债券编码236792</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>30Y</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>62.41</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>文档内含6处债券简称但只切分出2个债券名称分块，疑似OCR识别丢失部分'债券名称'标签导致相邻债券字段串块，本行金额/期限/利率可能并非同一支债券，需人工核对原文</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
         <is>
           <t>http://czt.henan.gov.cn/2026/07-23/3378602.html</t>
         </is>
